--- a/artfynd/A 62575-2021 artfynd.xlsx
+++ b/artfynd/A 62575-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62575-2021 artfynd.xlsx
+++ b/artfynd/A 62575-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>37425690</v>
+        <v>37563731</v>
       </c>
       <c r="B2" t="n">
-        <v>56400</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R2" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S2" t="n">
         <v>105</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1962-04-22</t>
+          <t>1963-05-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -759,17 +754,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1962-04-22</t>
+          <t>1963-05-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Obs: IJ</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Ornitologiska Klubben Eskilstuna</t>
+          <t>Tony Haglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,16 +793,11 @@
         <v>37590739</v>
       </c>
       <c r="B3" t="n">
-        <v>56295</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -849,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R3" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S3" t="n">
         <v>105</v>
@@ -930,32 +915,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>37563731</v>
+        <v>37358784</v>
       </c>
       <c r="B4" t="n">
-        <v>56285</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -965,7 +945,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande NO</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R4" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S4" t="n">
         <v>105</v>
@@ -1004,7 +989,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1963-05-26</t>
+          <t>1964-04-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1014,7 +999,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1963-05-26</t>
+          <t>1964-04-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1050,15 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>37327855</v>
+        <v>37425690</v>
       </c>
       <c r="B5" t="n">
-        <v>55607</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1088,21 +1068,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormossen, Hörningssjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R5" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S5" t="n">
         <v>105</v>
@@ -1129,7 +1104,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1966-05-17</t>
+          <t>1962-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1139,7 +1114,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1966-05-17</t>
+          <t>1962-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1149,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Obs: KEA</t>
+          <t>Obs: IJ</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,37 +1155,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>37545061</v>
+        <v>37585683</v>
       </c>
       <c r="B6" t="n">
-        <v>57063</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>100065</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1218,16 +1188,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormossen, Hörningssjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R6" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S6" t="n">
         <v>105</v>
@@ -1254,7 +1229,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1963-01-31</t>
+          <t>1971-04-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1264,7 +1239,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1963-01-31</t>
+          <t>1971-04-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1274,7 +1249,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Antal ej angivet Obs: IJ</t>
+          <t>Häckning ? Obs: YL</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,15 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>37640298</v>
+        <v>37606418</v>
       </c>
       <c r="B7" t="n">
-        <v>57067</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,16 +1291,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103057</v>
+        <v>100090</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1340,7 +1310,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R7" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S7" t="n">
         <v>105</v>
@@ -1379,7 +1349,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1962-01-31</t>
+          <t>1958-09-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1389,7 +1359,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1962-01-31</t>
+          <t>1958-09-24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1399,7 +1369,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs: PGH</t>
+          <t>Obs: IS</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,15 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37637610</v>
+        <v>37615924</v>
       </c>
       <c r="B8" t="n">
-        <v>55833</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1430,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R8" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S8" t="n">
         <v>105</v>
@@ -1504,7 +1479,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1959-05-10</t>
+          <t>1957-06-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1514,7 +1489,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1959-05-10</t>
+          <t>1957-06-02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1524,7 +1499,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Noterad Antal ej angivet Obs: IJ, SM</t>
+          <t>Obs: IJ</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,52 +1530,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>37631019</v>
+        <v>37485085</v>
       </c>
       <c r="B9" t="n">
-        <v>55802</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102952</v>
+        <v>102119</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>pulli</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1609,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R9" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S9" t="n">
         <v>105</v>
@@ -1659,7 +1624,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 kull 4 ungar Observatör ej angiven</t>
+          <t>Obs: IJ</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,53 +1655,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>60293347</v>
+        <v>37327855</v>
       </c>
       <c r="B10" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103035</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormossen, Hörningssjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R10" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S10" t="n">
         <v>105</v>
@@ -1763,22 +1729,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
+          <t>1966-05-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
+          <t>1966-05-17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Obs: KEA</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,27 +1764,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Claesson</t>
+          <t>Ornitologiska Klubben Eskilstuna</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Claesson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>OKE:s arkiv</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>60293362</v>
+        <v>37569467</v>
       </c>
       <c r="B11" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,37 +1791,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormossen, Hörningssjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575768.6168283764</v>
+        <v>575769</v>
       </c>
       <c r="R11" t="n">
-        <v>6578458.300872608</v>
+        <v>6578458</v>
       </c>
       <c r="S11" t="n">
         <v>105</v>
@@ -1878,22 +1854,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
+          <t>1964-03-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
+          <t>1964-03-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Obs: BA</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1908,15 +1889,849 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>OKE:s arkiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>37631019</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57317</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsvipa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vanellus vanellus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stormossen, Hörningssjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575769</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6578458</v>
+      </c>
+      <c r="S12" t="n">
+        <v>105</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1957-06-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1957-06-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 kull 4 ungar Observatör ej angiven</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>OKE:s arkiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>37604785</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stormossen, Hörningssjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575769</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6578458</v>
+      </c>
+      <c r="S13" t="n">
+        <v>105</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1967-04-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1967-04-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Obs: AL</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>OKE:s arkiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>37470392</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stormossen, Hörningssjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>575769</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6578458</v>
+      </c>
+      <c r="S14" t="n">
+        <v>105</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1967-04-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1967-04-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Obs: AL</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>OKE:s arkiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>60293362</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormossen, Hörningssjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>575769</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6578458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>105</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Magnus Claesson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Magnus Claesson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>37545061</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stormossen, Hörningssjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>575769</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6578458</v>
+      </c>
+      <c r="S16" t="n">
+        <v>105</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1963-01-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1963-01-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Antal ej angivet Obs: IJ</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>OKE:s arkiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>37640298</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stormossen, Hörningssjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>575769</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6578458</v>
+      </c>
+      <c r="S17" t="n">
+        <v>105</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1962-01-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1962-01-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Obs: PGH</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Ornitologiska Klubben Eskilstuna</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>OKE:s arkiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>60293347</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stormossen, Hörningssjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>575769</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6578458</v>
+      </c>
+      <c r="S18" t="n">
+        <v>105</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gillberga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2016-06-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Claesson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Claesson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62575-2021 artfynd.xlsx
+++ b/artfynd/A 62575-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37563731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37590739</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37358784</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37425690</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37585683</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1397,6 +1427,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37606418</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37615924</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1652,6 +1692,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37485085</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1777,6 +1822,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37327855</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1902,6 +1952,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37569467</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2032,6 +2087,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37631019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2152,6 +2212,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37604785</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2270,6 +2335,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>OKE:s arkiv</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37470392</t>
         </is>
       </c>
     </row>
@@ -2382,6 +2452,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60293362</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2502,6 +2577,11 @@
           <t>OKE:s arkiv</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37545061</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2620,6 +2700,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>OKE:s arkiv</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/37640298</t>
         </is>
       </c>
     </row>
@@ -2732,8 +2817,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60293347</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>